--- a/Manual-Testing/BugReport.xlsx
+++ b/Manual-Testing/BugReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLESSY B SHERIN\OneDrive\Desktop\QA-Portfolio\Manual-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A466B4FC-E0EC-4479-9A2D-B2B2F83D771A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C81F920-41A5-459D-A241-FC3CC086A87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" xr2:uid="{A844FD75-4DF3-4B40-B9C5-F87D319A3CF5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A844FD75-4DF3-4B40-B9C5-F87D319A3CF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1013,7 +1013,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
